--- a/sample_data/tests/02 - Work instruction.xlsx
+++ b/sample_data/tests/02 - Work instruction.xlsx
@@ -7,17 +7,30 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Work instruction" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Work Instruction" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="WI_SERIES">'Work instruction'!$B$4</definedName>
-    <definedName name="WI_SAMPLE">'Work instruction'!$E$4</definedName>
-    <definedName name="WI_CUSTOMER">'Work instruction'!$B$6</definedName>
-    <definedName name="WI_START">'Work instruction'!$E$6</definedName>
-    <definedName name="WI_COMPLETED">'Work instruction'!$B$7</definedName>
-    <definedName name="WI_STANDARD">'Work instruction'!$E$7</definedName>
-    <definedName name="WI_ALLOTTED">'Work instruction'!$B$8</definedName>
-    <definedName name="WI_ENGINEER">'Work instruction'!$E$8</definedName>
+    <definedName name="WI2_SERIES">'Work Instruction'!$E$8</definedName>
+    <definedName name="WI2_SAMPLE">'Work Instruction'!$E$9</definedName>
+    <definedName name="WI2_CUSTOMER">'Work Instruction'!$E$10</definedName>
+    <definedName name="WI2_CUSTOMER_REF">'Work Instruction'!$E$11</definedName>
+    <definedName name="WI2_DESCRIPTION">'Work Instruction'!$E$12</definedName>
+    <definedName name="WI2_MOUNTING">'Work Instruction'!$E$13</definedName>
+    <definedName name="WI2_SPECIAL">'Work Instruction'!$E$14</definedName>
+    <definedName name="WI2_START">'Work Instruction'!$E$15</definedName>
+    <definedName name="WI2_REQUIREMENT">'Work Instruction'!$E$16</definedName>
+    <definedName name="WI2_TESTS_REQUIRED">'Work Instruction'!$E$17</definedName>
+    <definedName name="WI2_STANDARD">'Work Instruction'!$E$18</definedName>
+    <definedName name="WI2_STANDARD_LATEST">'Work Instruction'!$E$19</definedName>
+    <definedName name="WI2_DEVIATION">'Work Instruction'!$E$20</definedName>
+    <definedName name="WI2_ALLOTTED">'Work Instruction'!$E$21</definedName>
+    <definedName name="WI2_SIG_HOD">'Work Instruction'!$A$22</definedName>
+    <definedName name="WI2_COMPLETED">'Work Instruction'!$E$25</definedName>
+    <definedName name="WI2_PERFORMED_BY">'Work Instruction'!$E$26</definedName>
+    <definedName name="WI2_ENGINEER">'Work Instruction'!$E$27</definedName>
+    <definedName name="WI2_DEVIATIONS_NOTICED">'Work Instruction'!$E$28</definedName>
+    <definedName name="WI2_DISCREPANCIES">'Work Instruction'!$E$29</definedName>
+    <definedName name="WI2_SIG_ENGINEER">'Work Instruction'!$A$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,8 +38,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd-mm-yyyy"/>
+  </numFmts>
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,16 +50,39 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="13"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="6"/>
     </font>
     <font>
       <i val="1"/>
-      <color rgb="0056667F"/>
+      <color rgb="001C3D6E"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="00333333"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -53,11 +91,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00EAF3FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF1F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFFBEA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -79,19 +127,97 @@
         <color rgb="009AA8BD"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="009AA8BD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009AA8BD"/>
+      </right>
+      <top style="thin">
+        <color rgb="009AA8BD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="009AA8BD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009AA8BD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009AA8BD"/>
+      </right>
+      <top style="thin">
+        <color rgb="009AA8BD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009AA8BD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -455,119 +581,552 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="10.5" customWidth="1" min="1" max="1"/>
+    <col width="10.5" customWidth="1" min="2" max="2"/>
+    <col width="10.5" customWidth="1" min="3" max="3"/>
+    <col width="10.5" customWidth="1" min="4" max="4"/>
+    <col width="10.5" customWidth="1" min="5" max="5"/>
+    <col width="10.5" customWidth="1" min="6" max="6"/>
+    <col width="10.5" customWidth="1" min="7" max="7"/>
+    <col width="10.5" customWidth="1" min="8" max="8"/>
+    <col width="10.5" customWidth="1" min="9" max="9"/>
+    <col width="10.5" customWidth="1" min="10" max="10"/>
+    <col width="10.5" customWidth="1" min="11" max="11"/>
+    <col width="10.5" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" hidden="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Work instruction</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>Aletheia template work v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CPRI Short Circuit Laboratory - form: Aletheia template work (version 1). Fill the yellow cells only; do not move or rename them.</t>
+          <t>Fill in the yellow cells as on the paper logsheet. Grey cells are printed text or are calculated; they are locked. Choose from the list where a cell offers one; readings must be numbers and dates must be dates (dd-mm-yyyy). Leave a cell empty if the value is not on the sheet: it is recorded as NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>CENTRAL POWER RESEARCH INSTITUTE</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Test series no. (as written)</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Name of the Unit / Division : SHORT CIRCUIT LABORATORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Format No. : CPRI/QAF/02
+Revision No. 02
+Revision Date : 28/10/2019</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Issue No. 01
+Date of Issue : 15-11-2005
+Sheet 1 of 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Work Instruction</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Test series Number (Where applicable)</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>CPRIBLRSCL25T1654</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Sample code no. (as written)</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F8" s="12" t="n"/>
+      <c r="G8" s="12" t="n"/>
+      <c r="H8" s="12" t="n"/>
+      <c r="I8" s="12" t="n"/>
+      <c r="J8" s="12" t="n"/>
+      <c r="K8" s="12" t="n"/>
+      <c r="L8" s="13" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Sample Code Number</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>HVD25S0847</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Customer</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="13" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Name of Customer</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>M/s. A.P. Transformers, Chennai</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Test started</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>28-10-2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Test completed</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>18-11-2025</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n"/>
+      <c r="H10" s="12" t="n"/>
+      <c r="I10" s="12" t="n"/>
+      <c r="J10" s="12" t="n"/>
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="13" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Customer Reference Number</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="12" t="n"/>
+      <c r="H11" s="12" t="n"/>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="12" t="n"/>
+      <c r="K11" s="12" t="n"/>
+      <c r="L11" s="13" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Description of Test Sample</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n"/>
+      <c r="H12" s="12" t="n"/>
+      <c r="I12" s="12" t="n"/>
+      <c r="J12" s="12" t="n"/>
+      <c r="K12" s="12" t="n"/>
+      <c r="L12" s="13" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Specific Instructions for mounting and Connections, if any</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="12" t="n"/>
+      <c r="I13" s="12" t="n"/>
+      <c r="J13" s="12" t="n"/>
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="13" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Special Instructions</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="12" t="n"/>
+      <c r="H14" s="12" t="n"/>
+      <c r="I14" s="12" t="n"/>
+      <c r="J14" s="12" t="n"/>
+      <c r="K14" s="12" t="n"/>
+      <c r="L14" s="13" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Date of Test</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="14" t="n">
+        <v>45958</v>
+      </c>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
+      <c r="H15" s="12" t="n"/>
+      <c r="I15" s="12" t="n"/>
+      <c r="J15" s="12" t="n"/>
+      <c r="K15" s="12" t="n"/>
+      <c r="L15" s="13" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Customer Requirement</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="13" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Name of Test or Tests Required</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="13" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Reference Standard for the Test</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>IS 1180 (latest: yes)</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Allotted to</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n"/>
+      <c r="H18" s="12" t="n"/>
+      <c r="I18" s="12" t="n"/>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="13" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Whether Standard used is latest</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+      <c r="H19" s="12" t="n"/>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="13" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Deviation / Change from Standard</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="12" t="n"/>
+      <c r="J20" s="12" t="n"/>
+      <c r="K20" s="12" t="n"/>
+      <c r="L20" s="13" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Work Allotted to</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>Sh. NMR / Sh. NK / Mr. Utley</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Test engineer</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="12" t="n"/>
+      <c r="H21" s="12" t="n"/>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="13" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="12" t="n"/>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="12" t="n"/>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="12" t="n"/>
+      <c r="L22" s="13" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Signature Test In Charge / HOD with Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Work Completed on</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="14" t="n">
+        <v>45979</v>
+      </c>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="13" t="n"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Name &amp; Signature of the Test Engineer who performed the work</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="13" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Test Engineer Responsible for Report</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>P. Naveenkumar</t>
         </is>
       </c>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="13" t="n"/>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Deviations Noticed during the Testing / Calibration</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="12" t="n"/>
+      <c r="G28" s="12" t="n"/>
+      <c r="H28" s="12" t="n"/>
+      <c r="I28" s="12" t="n"/>
+      <c r="J28" s="12" t="n"/>
+      <c r="K28" s="12" t="n"/>
+      <c r="L28" s="13" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Recording of sorting out the discrepancies</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="13" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="n"/>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="13" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Name &amp; signature of Test Engineer with Date</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
+  <mergeCells count="48">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="E12:L12"/>
+    <mergeCell ref="E18:L18"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E21:L21"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="E14:L14"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="E8:L8"/>
+    <mergeCell ref="E17:L17"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="E20:L20"/>
+    <mergeCell ref="G5:L5"/>
+    <mergeCell ref="E29:L29"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="E10:L10"/>
+    <mergeCell ref="E28:L28"/>
+    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="E13:L13"/>
+    <mergeCell ref="E19:L19"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="E9:L9"/>
+    <mergeCell ref="E15:L15"/>
+    <mergeCell ref="E11:L11"/>
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="E27:L27"/>
+    <mergeCell ref="E26:L26"/>
+    <mergeCell ref="A30:L30"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="E25:L25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="E16:L16"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="E15:L15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a date (dd-mm-yyyy)" type="date" operator="greaterThanOrEqual">
+      <formula1>36526</formula1>
+    </dataValidation>
+    <dataValidation sqref="E19:L19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Choose one of the listed values" type="list" errorStyle="stop">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E25:L25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a date (dd-mm-yyyy)" type="date" operator="greaterThanOrEqual">
+      <formula1>36526</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>